--- a/src/data/inputs/sources-guide.xlsx
+++ b/src/data/inputs/sources-guide.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ben/Documents/bruegel/data_new/WORKING/ENERGY/gas-demand/src/data/inputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://timera-my.sharepoint.com/personal/rory_perkins_timera-energy_com/Documents/Documents/GitHub/gas-demand/src/data/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C957E779-BB76-6844-A944-C09093A3610B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{C957E779-BB76-6844-A944-C09093A3610B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A00EE651-2940-49E8-8F9D-6BD372A95A4F}"/>
   <bookViews>
-    <workbookView xWindow="4300" yWindow="740" windowWidth="24920" windowHeight="16940" xr2:uid="{8D505957-1A62-5F40-9BA7-A9611DA49F6F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8D505957-1A62-5F40-9BA7-A9611DA49F6F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$29</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="56">
   <si>
     <t>AT</t>
   </si>
@@ -198,13 +202,19 @@
   </si>
   <si>
     <t>eurostat</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>EU27_2020</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -228,15 +238,25 @@
       <sz val="12"/>
       <color rgb="FFC00000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -245,12 +265,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -258,18 +284,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -604,538 +650,1001 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A50B2BC-7E94-1742-82E2-4355077DD989}">
-  <dimension ref="A1:K29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L46"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.5" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="30.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="9" max="9" width="30.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B1" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
+      <c r="A2" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="7" t="str">
+        <f>VLOOKUP(A2,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>AT</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="str">
+        <f>VLOOKUP(A3,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>BE</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="7" t="str">
+        <f>VLOOKUP(A4,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>BG</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="7" t="str">
+        <f>VLOOKUP(A5,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>HR</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="7" t="str">
+        <f>VLOOKUP(A6,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>CZ</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="7" t="str">
+        <f>VLOOKUP(A7,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>DK</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="7" t="str">
+        <f>VLOOKUP(A8,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>EE</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="7" t="str">
+        <f>VLOOKUP(A9,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>ES</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="7" t="str">
+        <f>VLOOKUP(A10,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>FI</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="7" t="str">
+        <f>VLOOKUP(A11,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>FR</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="7" t="str">
+        <f>VLOOKUP(A12,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>DE</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="7" t="str">
+        <f>VLOOKUP(A13,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>GR</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="7" t="str">
+        <f>VLOOKUP(A14,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>HU</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="7" t="str">
+        <f>VLOOKUP(A15,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>IE</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="7" t="str">
+        <f>VLOOKUP(A16,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>IT</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="7" t="str">
+        <f>VLOOKUP(A17,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>LV</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="3"/>
+      <c r="H17" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="7" t="str">
+        <f>VLOOKUP(A18,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>LT</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="3"/>
+      <c r="H18" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="7" t="str">
+        <f>VLOOKUP(A19,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>LU</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="7" t="str">
+        <f>VLOOKUP(A20,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>NL</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="7" t="str">
+        <f>VLOOKUP(A21,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>PL</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="3"/>
+      <c r="H21" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="7" t="str">
+        <f>VLOOKUP(A22,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>PT</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="7" t="str">
+        <f>VLOOKUP(A23,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>RO</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="7" t="str">
+        <f>VLOOKUP(A24,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>SK</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="3"/>
+      <c r="H24" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="7" t="str">
+        <f>VLOOKUP(A25,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>SI</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="3"/>
+      <c r="H25" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="7" t="str">
+        <f>VLOOKUP(A26,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>SE</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="3"/>
+      <c r="H26" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="7" t="e">
+        <f>VLOOKUP(A27,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="7" t="str">
+        <f>VLOOKUP(A28,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>CY</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="7" t="str">
+        <f>VLOOKUP(A29,Sheet2!$A$2:$A$29,1,FALSE)</f>
+        <v>MT</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4">
+      <c r="C33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D33" t="str">
+        <f>VLOOKUP(C33,$A$2:$C$27,2,FALSE)</f>
+        <v>BE</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4">
+      <c r="C34" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" t="str">
+        <f t="shared" ref="D34:D46" si="0">VLOOKUP(C34,$A$2:$C$27,2,FALSE)</f>
+        <v>CZ</v>
+      </c>
+    </row>
+    <row r="35" spans="3:4">
+      <c r="C35" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" t="str">
+        <f t="shared" si="0"/>
+        <v>FI</v>
+      </c>
+    </row>
+    <row r="36" spans="3:4">
+      <c r="C36" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" t="str">
+        <f t="shared" si="0"/>
+        <v>GR</v>
+      </c>
+    </row>
+    <row r="37" spans="3:4">
+      <c r="C37" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" t="str">
+        <f t="shared" si="0"/>
+        <v>HU</v>
+      </c>
+    </row>
+    <row r="38" spans="3:4">
+      <c r="C38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D38" t="str">
+        <f t="shared" si="0"/>
+        <v>IE</v>
+      </c>
+    </row>
+    <row r="39" spans="3:4">
+      <c r="C39" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" t="str">
+        <f t="shared" si="0"/>
+        <v>IT</v>
+      </c>
+    </row>
+    <row r="40" spans="3:4">
+      <c r="C40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D40" t="str">
+        <f t="shared" si="0"/>
+        <v>LT</v>
+      </c>
+    </row>
+    <row r="41" spans="3:4">
+      <c r="C41" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D41" t="str">
+        <f t="shared" si="0"/>
+        <v>LU</v>
+      </c>
+    </row>
+    <row r="42" spans="3:4">
+      <c r="C42" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D42" t="str">
+        <f t="shared" si="0"/>
+        <v>NL</v>
+      </c>
+    </row>
+    <row r="43" spans="3:4">
+      <c r="C43" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D43" t="str">
+        <f t="shared" si="0"/>
+        <v>PT</v>
+      </c>
+    </row>
+    <row r="44" spans="3:4">
+      <c r="C44" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D44" t="str">
+        <f t="shared" si="0"/>
+        <v>RO</v>
+      </c>
+    </row>
+    <row r="45" spans="3:4">
+      <c r="C45" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" t="str">
+        <f t="shared" si="0"/>
+        <v>SE</v>
+      </c>
+    </row>
+    <row r="46" spans="3:4">
+      <c r="C46" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D46" t="str">
+        <f t="shared" si="0"/>
+        <v>SK</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J29" xr:uid="{2A50B2BC-7E94-1742-82E2-4355077DD989}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA4B6D96-AC30-460A-8A74-497B61512CA2}">
+  <dimension ref="A1:A29"/>
+  <sheetFormatPr defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="9.9140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
         <v>34</v>
       </c>
-      <c r="B9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
         <v>17</v>
       </c>
-      <c r="B10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="I12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
         <v>20</v>
       </c>
-      <c r="B13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>9</v>
-      </c>
-      <c r="H14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
         <v>22</v>
       </c>
-      <c r="B15" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" t="s">
-        <v>36</v>
-      </c>
-      <c r="H15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="H16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
         <v>24</v>
       </c>
-      <c r="B17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H17" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H18" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K20" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
         <v>29</v>
       </c>
-      <c r="B21" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H21" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>9</v>
-      </c>
-      <c r="H22" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>9</v>
-      </c>
-      <c r="H23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
         <v>32</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H25" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H26" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" t="s">
-        <v>39</v>
-      </c>
-      <c r="D27" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27" t="s">
-        <v>39</v>
-      </c>
-      <c r="H27" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
